--- a/03_Outputs/Agua_Bosques_Turismo/05_Economia/economia.xlsx
+++ b/03_Outputs/Agua_Bosques_Turismo/05_Economia/economia.xlsx
@@ -15446,10 +15446,8 @@
       <c r="F36" s="118">
         <v>4.41182925134159</v>
       </c>
-      <c r="G36" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G36" s="120">
+        <v>0.0936180992388625</v>
       </c>
       <c r="H36" s="122">
         <v>1.16288460220095</v>
@@ -15687,7 +15685,7 @@
         <v>443.654251804697</v>
       </c>
       <c r="G40" s="121">
-        <v>1.07545101881368</v>
+        <v>1.16906911805254</v>
       </c>
       <c r="H40" s="123">
         <v>261.001751296806</v>
@@ -16158,10 +16156,8 @@
       <c r="F48" s="118">
         <v>13.1771335731762</v>
       </c>
-      <c r="G48" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G48" s="120">
+        <v>0.0137722957218968</v>
       </c>
       <c r="H48" s="122">
         <v>3.49996339892534</v>
@@ -16222,10 +16218,8 @@
       <c r="G49" s="120">
         <v>0</v>
       </c>
-      <c r="H49" s="122" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H49" s="122">
+        <v>0.0429904502665356</v>
       </c>
       <c r="I49" s="124">
         <v>5.52830891885819</v>
@@ -16460,10 +16454,10 @@
         <v>597.67200657822</v>
       </c>
       <c r="G53" s="121">
-        <v>0.291325546819661</v>
+        <v>0.305097842541558</v>
       </c>
       <c r="H53" s="123">
-        <v>239.827403964004</v>
+        <v>239.870394414271</v>
       </c>
       <c r="I53" s="125">
         <v>294.453493548196</v>
@@ -16636,10 +16630,8 @@
       <c r="F56" s="118">
         <v>12.2012000615695</v>
       </c>
-      <c r="G56" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G56" s="120">
+        <v>0.0853516955650943</v>
       </c>
       <c r="H56" s="122">
         <v>1.76696986052996</v>
@@ -16995,10 +16987,8 @@
       <c r="G62" s="120">
         <v>0</v>
       </c>
-      <c r="H62" s="122" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="H62" s="122">
+        <v>0.0403631540791599</v>
       </c>
       <c r="I62" s="124">
         <v>5.43737639183627</v>
@@ -17171,10 +17161,8 @@
       <c r="F65" s="118">
         <v>78.8884763985566</v>
       </c>
-      <c r="G65" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G65" s="120">
+        <v>0.0117581444766808</v>
       </c>
       <c r="H65" s="122">
         <v>4.04347202582466</v>
@@ -17235,10 +17223,10 @@
         <v>488.704078671973</v>
       </c>
       <c r="G66" s="121">
-        <v>0.923794377079652</v>
+        <v>1.02090421712143</v>
       </c>
       <c r="H66" s="123">
-        <v>252.143178463749</v>
+        <v>252.183541617828</v>
       </c>
       <c r="I66" s="125">
         <v>290.748796379334</v>
@@ -17411,10 +17399,8 @@
       <c r="F69" s="118">
         <v>12.3671408149064</v>
       </c>
-      <c r="G69" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G69" s="120">
+        <v>0.0538713364489053</v>
       </c>
       <c r="H69" s="122">
         <v>1.6161540303618</v>
@@ -17649,10 +17635,8 @@
       <c r="F73" s="118">
         <v>223.816987473527</v>
       </c>
-      <c r="G73" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G73" s="120">
+        <v>0.00353386643239794</v>
       </c>
       <c r="H73" s="122">
         <v>4.52216174803431</v>
@@ -17828,10 +17812,8 @@
       <c r="F76" s="118">
         <v>4.91624709670881</v>
       </c>
-      <c r="G76" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G76" s="120">
+        <v>0.0366374447963848</v>
       </c>
       <c r="H76" s="122">
         <v>1.99557989114134</v>
@@ -17948,10 +17930,8 @@
       <c r="F78" s="118">
         <v>79.4978427766863</v>
       </c>
-      <c r="G78" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G78" s="120">
+        <v>0.0785441678614972</v>
       </c>
       <c r="H78" s="122">
         <v>3.95295771383126</v>
@@ -18012,7 +17992,7 @@
         <v>521.388253927508</v>
       </c>
       <c r="G79" s="121">
-        <v>1.46157782965783</v>
+        <v>1.63416464519701</v>
       </c>
       <c r="H79" s="123">
         <v>348.988048009168</v>
@@ -18188,10 +18168,8 @@
       <c r="F82" s="118">
         <v>8.21274579283637</v>
       </c>
-      <c r="G82" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G82" s="120">
+        <v>0.0327965182453558</v>
       </c>
       <c r="H82" s="122">
         <v>1.78855580807047</v>
@@ -18603,10 +18581,8 @@
       <c r="F89" s="118">
         <v>7.57710970684432</v>
       </c>
-      <c r="G89" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G89" s="120">
+        <v>0.00258225920379651</v>
       </c>
       <c r="H89" s="122">
         <v>3.07469123771864</v>
@@ -18785,7 +18761,7 @@
         <v>563.690243781199</v>
       </c>
       <c r="G92" s="121">
-        <v>4.27784902795072</v>
+        <v>4.31322780539987</v>
       </c>
       <c r="H92" s="123">
         <v>409.569782779261</v>
@@ -18961,10 +18937,8 @@
       <c r="F95" s="118">
         <v>13.6191447392228</v>
       </c>
-      <c r="G95" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G95" s="120">
+        <v>0.0961056396147389</v>
       </c>
       <c r="H95" s="122">
         <v>0.813650742903621</v>
@@ -19556,7 +19530,7 @@
         <v>569.853681268357</v>
       </c>
       <c r="G105" s="121">
-        <v>2.36256096680231</v>
+        <v>2.45866660641705</v>
       </c>
       <c r="H105" s="123">
         <v>488.646664294023</v>
@@ -20204,10 +20178,8 @@
       <c r="F116" s="118">
         <v>6.38513054921115</v>
       </c>
-      <c r="G116" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G116" s="120">
+        <v>0.0397297683620049</v>
       </c>
       <c r="H116" s="122">
         <v>2.37250845039526</v>
@@ -20327,7 +20299,7 @@
         <v>580.929751727882</v>
       </c>
       <c r="G118" s="121">
-        <v>2.91549660699149</v>
+        <v>2.9552263753535</v>
       </c>
       <c r="H118" s="123">
         <v>520.737182312499</v>
@@ -20798,10 +20770,8 @@
       <c r="F126" s="118">
         <v>16.2595810965259</v>
       </c>
-      <c r="G126" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G126" s="120">
+        <v>0.0130057107787627</v>
       </c>
       <c r="H126" s="122">
         <v>13.6448535085141</v>
@@ -21036,10 +21006,8 @@
       <c r="F130" s="118">
         <v>122.003469148605</v>
       </c>
-      <c r="G130" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G130" s="120">
+        <v>0.00540712945285103</v>
       </c>
       <c r="H130" s="122">
         <v>9.35339351239766</v>
@@ -21100,7 +21068,7 @@
         <v>619.091538915446</v>
       </c>
       <c r="G131" s="121">
-        <v>0.761832493462461</v>
+        <v>0.780245333694074</v>
       </c>
       <c r="H131" s="123">
         <v>520.047146290828</v>
@@ -25051,7 +25019,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.761832493462461</v>
+        <v>0.780245333694074</v>
       </c>
     </row>
     <row r="4">
